--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61.25868436064682</v>
+        <v>9.954536208605107</v>
       </c>
       <c r="D2" t="n">
-        <v>8.247812196920172</v>
+        <v>1.340269481999528</v>
       </c>
       <c r="E2" t="n">
-        <v>17.75621153923461</v>
+        <v>2.885384375125625</v>
       </c>
       <c r="F2" t="n">
-        <v>18.30045376671283</v>
+        <v>2.973823737090835</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.18593940214789</v>
+        <v>6.367715152849032</v>
       </c>
       <c r="D3" t="n">
-        <v>16.83664511046572</v>
+        <v>2.73595483045068</v>
       </c>
       <c r="E3" t="n">
-        <v>17.75621153923461</v>
+        <v>2.885384375125625</v>
       </c>
       <c r="F3" t="n">
-        <v>18.30045376671283</v>
+        <v>2.973823737090835</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.80533627730143</v>
+        <v>8.743367145061482</v>
       </c>
       <c r="D4" t="n">
-        <v>47.5478784690748</v>
+        <v>7.726530251224655</v>
       </c>
       <c r="E4" t="n">
-        <v>17.75621153923461</v>
+        <v>2.885384375125625</v>
       </c>
       <c r="F4" t="n">
-        <v>18.30045376671283</v>
+        <v>2.973823737090835</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.90998126919467</v>
+        <v>5.022871956244134</v>
       </c>
       <c r="D5" t="n">
-        <v>9.656603957913983</v>
+        <v>1.569198143161022</v>
       </c>
       <c r="E5" t="n">
-        <v>17.75621153923461</v>
+        <v>2.885384375125625</v>
       </c>
       <c r="F5" t="n">
-        <v>18.30045376671283</v>
+        <v>2.973823737090835</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.82388772889071</v>
+        <v>5.82138175594474</v>
       </c>
       <c r="D6" t="n">
-        <v>29.84978572460262</v>
+        <v>4.850590180247925</v>
       </c>
       <c r="E6" t="n">
-        <v>17.75621153923461</v>
+        <v>2.885384375125625</v>
       </c>
       <c r="F6" t="n">
-        <v>18.30045376671283</v>
+        <v>2.973823737090835</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.76839075239253</v>
+        <v>2.399863497263787</v>
       </c>
       <c r="D7" t="n">
-        <v>13.72684949482394</v>
+        <v>2.23061304290889</v>
       </c>
       <c r="E7" t="n">
-        <v>17.75621153923461</v>
+        <v>2.885384375125625</v>
       </c>
       <c r="F7" t="n">
-        <v>18.30045376671283</v>
+        <v>2.973823737090835</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>6.402996345867015</v>
+        <v>1.04048690620339</v>
       </c>
       <c r="D8" t="n">
-        <v>4.618635474984806</v>
+        <v>0.750528264685031</v>
       </c>
       <c r="E8" t="n">
-        <v>17.75621153923461</v>
+        <v>2.885384375125625</v>
       </c>
       <c r="F8" t="n">
-        <v>18.30045376671283</v>
+        <v>2.973823737090835</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.46289618125753</v>
+        <v>3.162720629454349</v>
       </c>
       <c r="D9" t="n">
-        <v>17.74167009336686</v>
+        <v>2.883021390172115</v>
       </c>
       <c r="E9" t="n">
-        <v>17.75621153923461</v>
+        <v>2.885384375125625</v>
       </c>
       <c r="F9" t="n">
-        <v>18.30045376671283</v>
+        <v>2.973823737090835</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.42126741981357</v>
+        <v>3.968455955719706</v>
       </c>
       <c r="D10" t="n">
-        <v>22.9297327420708</v>
+        <v>3.726081570586505</v>
       </c>
       <c r="E10" t="n">
-        <v>17.75621153923461</v>
+        <v>2.885384375125625</v>
       </c>
       <c r="F10" t="n">
-        <v>18.30045376671283</v>
+        <v>2.973823737090835</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>48.23908128102727</v>
+        <v>7.838850708166932</v>
       </c>
       <c r="D11" t="n">
-        <v>47.81899822665829</v>
+        <v>7.770587211831972</v>
       </c>
       <c r="E11" t="n">
-        <v>17.75621153923461</v>
+        <v>2.885384375125625</v>
       </c>
       <c r="F11" t="n">
-        <v>18.30045376671283</v>
+        <v>2.973823737090835</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>47.70159698329982</v>
+        <v>7.751509509786222</v>
       </c>
       <c r="D12" t="n">
-        <v>46.04441550121651</v>
+        <v>7.482217518947683</v>
       </c>
       <c r="E12" t="n">
-        <v>17.75621153923461</v>
+        <v>2.885384375125625</v>
       </c>
       <c r="F12" t="n">
-        <v>18.30045376671283</v>
+        <v>2.973823737090835</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>64.06576501260827</v>
+        <v>10.41068681454884</v>
       </c>
       <c r="D13" t="n">
-        <v>62.4728188201091</v>
+        <v>10.15183305826773</v>
       </c>
       <c r="E13" t="n">
-        <v>17.75621153923461</v>
+        <v>2.885384375125625</v>
       </c>
       <c r="F13" t="n">
-        <v>18.30045376671283</v>
+        <v>2.973823737090835</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
